--- a/docs/reports/NVDA.xlsx
+++ b/docs/reports/NVDA.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWS Valuation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Price" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="6" state="visible" r:id="rId6"/>
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,20 +160,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,6 +179,7 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -570,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Technology · Standard (2-Stage FCFE) · generated 2026-07-08 · data: yfinance</t>
+          <t>Technology · Standard (forward multiples + DCF) · generated 2026-10-13 · data: Yahoo snapshot as of 2026-07-08</t>
         </is>
       </c>
     </row>
@@ -588,7 +585,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DCF value per share</t>
+          <t>DCF value per share (one lens)</t>
         </is>
       </c>
       <c r="B5" s="4">
@@ -610,11 +607,11 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Blended fair value (report)</t>
+          <t>12-month price target (report)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>179.1284419136819</v>
+        <v>270.3735326589133</v>
       </c>
     </row>
     <row r="8">
@@ -702,7 +699,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-08 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -744,16 +741,16 @@
           <t>Ordinary Shares Number</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>24661.36572</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>24640</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>24477</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>24304</v>
       </c>
     </row>
@@ -763,16 +760,16 @@
           <t>Share Issued</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="25" t="n">
         <v>24661.36572</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="25" t="n">
         <v>24640</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="25" t="n">
         <v>24477</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="25" t="n">
         <v>24304</v>
       </c>
     </row>
@@ -782,13 +779,13 @@
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <v>8956</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>7564</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>2429</v>
       </c>
     </row>
@@ -798,16 +795,16 @@
           <t>Total Debt</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>12031</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>11056</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>9982</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="25" t="n">
         <v>11040</v>
       </c>
     </row>
@@ -817,16 +814,16 @@
           <t>Tangible Book Value</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>16053</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>37436</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>73332</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>133155</v>
       </c>
     </row>
@@ -836,16 +833,16 @@
           <t>Invested Capital</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>33054</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>52687</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>87790</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>165761</v>
       </c>
     </row>
@@ -855,16 +852,16 @@
           <t>Working Capital</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>16510</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>33714</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>62079</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>93442</v>
       </c>
     </row>
@@ -874,16 +871,16 @@
           <t>Net Tangible Assets</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>16053</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>37436</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>73332</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>133155</v>
       </c>
     </row>
@@ -893,16 +890,16 @@
           <t>Capital Lease Obligations</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>1078</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>1347</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>1519</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>2572</v>
       </c>
     </row>
@@ -912,16 +909,16 @@
           <t>Common Stock Equity</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>22101</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>42978</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>79327</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>157293</v>
       </c>
     </row>
@@ -931,16 +928,16 @@
           <t>Total Capitalization</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>31804</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>51437</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>87790</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>164762</v>
       </c>
     </row>
@@ -950,16 +947,16 @@
           <t>Total Equity Gross Minority Interest</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>22101</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>42978</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>79327</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>157293</v>
       </c>
     </row>
@@ -969,16 +966,16 @@
           <t>Stockholders Equity</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>22101</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>42978</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>79327</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>157293</v>
       </c>
     </row>
@@ -988,16 +985,16 @@
           <t>Gains Losses Not Affecting Retained Earnings</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>-43</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>178</v>
       </c>
     </row>
@@ -1007,16 +1004,16 @@
           <t>Other Equity Adjustments</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>-43</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>178</v>
       </c>
     </row>
@@ -1026,7 +1023,7 @@
           <t>Treasury Stock</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1036,16 +1033,16 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>10171</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>29817</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>68038</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>146973</v>
       </c>
     </row>
@@ -1055,16 +1052,16 @@
           <t>Additional Paid In Capital</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>11971</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>13109</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>11237</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>10118</v>
       </c>
     </row>
@@ -1074,16 +1071,16 @@
           <t>Capital Stock</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1093,16 +1090,16 @@
           <t>Common Stock</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="25" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1112,16 +1109,16 @@
           <t>Preferred Stock</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1131,16 +1128,16 @@
           <t>Total Liabilities Net Minority Interest</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>19081</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>22750</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>32274</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>49510</v>
       </c>
     </row>
@@ -1150,16 +1147,16 @@
           <t>Total Non Current Liabilities Net Minority Interest</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>12518</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>12119</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>14227</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>17347</v>
       </c>
     </row>
@@ -1169,16 +1166,16 @@
           <t>Other Non Current Liabilities</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>63</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>65</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>195</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>381</v>
       </c>
     </row>
@@ -1188,16 +1185,16 @@
           <t>Tradeand Other Payables Non Current</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>1385</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>1441</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>2188</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>3958</v>
       </c>
     </row>
@@ -1207,16 +1204,16 @@
           <t>Non Current Deferred Liabilities</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>465</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>1035</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="25" t="n">
         <v>1862</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="25" t="n">
         <v>2967</v>
       </c>
     </row>
@@ -1226,16 +1223,16 @@
           <t>Non Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>218</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>573</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>976</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>1193</v>
       </c>
     </row>
@@ -1245,16 +1242,16 @@
           <t>Non Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>247</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>462</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>886</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>1774</v>
       </c>
     </row>
@@ -1264,16 +1261,16 @@
           <t>Long Term Debt And Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>10605</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>9578</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>9982</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>10041</v>
       </c>
     </row>
@@ -1283,16 +1280,16 @@
           <t>Long Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>902</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>1119</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>1519</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>2572</v>
       </c>
     </row>
@@ -1302,16 +1299,16 @@
           <t>Long Term Debt</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>9703</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>8459</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>8463</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="25" t="n">
         <v>7469</v>
       </c>
     </row>
@@ -1321,16 +1318,16 @@
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>6563</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>10631</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <v>18047</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="25" t="n">
         <v>32163</v>
       </c>
     </row>
@@ -1340,16 +1337,16 @@
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>69</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>199</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>897</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>1373</v>
       </c>
     </row>
@@ -1359,16 +1356,16 @@
           <t>Current Deferred Liabilities</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>354</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>764</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>837</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>1379</v>
       </c>
     </row>
@@ -1378,16 +1375,16 @@
           <t>Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>354</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>764</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>837</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="25" t="n">
         <v>1379</v>
       </c>
     </row>
@@ -1397,16 +1394,16 @@
           <t>Current Debt And Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>1426</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>1478</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="25" t="n">
         <v>288</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>999</v>
       </c>
     </row>
@@ -1416,16 +1413,16 @@
           <t>Current Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B41" s="29" t="n">
+      <c r="B41" s="25" t="n">
         <v>144</v>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>176</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>228</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>288</v>
       </c>
     </row>
@@ -1435,13 +1432,13 @@
           <t>Current Debt</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>1250</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>1250</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="25" t="n">
         <v>999</v>
       </c>
     </row>
@@ -1451,13 +1448,13 @@
           <t>Other Current Borrowings</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>1250</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>1250</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>999</v>
       </c>
     </row>
@@ -1467,16 +1464,16 @@
           <t>Current Provisions</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>108</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>415</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>1290</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>2807</v>
       </c>
     </row>
@@ -1486,16 +1483,16 @@
           <t>Payables And Accrued Expenses</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>4606</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>7775</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>15023</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>25605</v>
       </c>
     </row>
@@ -1505,16 +1502,16 @@
           <t>Current Accrued Expenses</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>2946</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>4780</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>7832</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>13124</v>
       </c>
     </row>
@@ -1524,16 +1521,16 @@
           <t>Payables</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>1660</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>2995</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="25" t="n">
         <v>7191</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="25" t="n">
         <v>12481</v>
       </c>
     </row>
@@ -1543,16 +1540,16 @@
           <t>Total Tax Payable</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>467</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>296</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>881</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>2669</v>
       </c>
     </row>
@@ -1562,16 +1559,16 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>1193</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>2699</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>6310</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>9812</v>
       </c>
     </row>
@@ -1581,16 +1578,16 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>41182</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>65728</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="25" t="n">
         <v>111601</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="25" t="n">
         <v>206803</v>
       </c>
     </row>
@@ -1600,16 +1597,16 @@
           <t>Total Non Current Assets</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>18109</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>21383</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>31475</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>81198</v>
       </c>
     </row>
@@ -1619,16 +1616,16 @@
           <t>Other Non Current Assets</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>145</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>357</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>3038</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>8301</v>
       </c>
     </row>
@@ -1638,16 +1635,16 @@
           <t>Non Current Prepaid Assets</t>
         </is>
       </c>
-      <c r="B53" s="29" t="n">
+      <c r="B53" s="25" t="n">
         <v>3509</v>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>3376</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="25" t="n">
         <v>2822</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="25" t="n">
         <v>2087</v>
       </c>
     </row>
@@ -1657,16 +1654,16 @@
           <t>Non Current Deferred Assets</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>3396</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>6081</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>10979</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="25" t="n">
         <v>13258</v>
       </c>
     </row>
@@ -1676,16 +1673,16 @@
           <t>Non Current Deferred Taxes Assets</t>
         </is>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>3396</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>6081</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="25" t="n">
         <v>10979</v>
       </c>
-      <c r="F55" s="29" t="n">
+      <c r="F55" s="25" t="n">
         <v>13258</v>
       </c>
     </row>
@@ -1695,7 +1692,7 @@
           <t>Non Current Accounts Receivable</t>
         </is>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="25" t="n">
         <v>750</v>
       </c>
     </row>
@@ -1705,16 +1702,16 @@
           <t>Investments And Advances</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="25" t="n">
         <v>299</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="25" t="n">
         <v>1321</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="25" t="n">
         <v>3387</v>
       </c>
-      <c r="F57" s="29" t="n">
+      <c r="F57" s="25" t="n">
         <v>22251</v>
       </c>
     </row>
@@ -1724,13 +1721,13 @@
           <t>Other Investments</t>
         </is>
       </c>
-      <c r="B58" s="29" t="n">
+      <c r="B58" s="25" t="n">
         <v>266</v>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="25" t="n">
         <v>299</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="25" t="n">
         <v>1546</v>
       </c>
     </row>
@@ -1740,13 +1737,13 @@
           <t>Investmentin Financial Assets</t>
         </is>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="25" t="n">
         <v>1321</v>
       </c>
-      <c r="E59" s="29" t="n">
+      <c r="E59" s="25" t="n">
         <v>3387</v>
       </c>
-      <c r="F59" s="29" t="n">
+      <c r="F59" s="25" t="n">
         <v>22251</v>
       </c>
     </row>
@@ -1756,13 +1753,13 @@
           <t>Available For Sale Securities</t>
         </is>
       </c>
-      <c r="D60" s="29" t="n">
+      <c r="D60" s="25" t="n">
         <v>1321</v>
       </c>
-      <c r="E60" s="29" t="n">
+      <c r="E60" s="25" t="n">
         <v>3387</v>
       </c>
-      <c r="F60" s="29" t="n">
+      <c r="F60" s="25" t="n">
         <v>22251</v>
       </c>
     </row>
@@ -1772,16 +1769,16 @@
           <t>Goodwill And Other Intangible Assets</t>
         </is>
       </c>
-      <c r="C61" s="29" t="n">
+      <c r="C61" s="25" t="n">
         <v>6048</v>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D61" s="25" t="n">
         <v>5542</v>
       </c>
-      <c r="E61" s="29" t="n">
+      <c r="E61" s="25" t="n">
         <v>5995</v>
       </c>
-      <c r="F61" s="29" t="n">
+      <c r="F61" s="25" t="n">
         <v>24138</v>
       </c>
     </row>
@@ -1791,16 +1788,16 @@
           <t>Other Intangible Assets</t>
         </is>
       </c>
-      <c r="C62" s="29" t="n">
+      <c r="C62" s="25" t="n">
         <v>1676</v>
       </c>
-      <c r="D62" s="29" t="n">
+      <c r="D62" s="25" t="n">
         <v>1112</v>
       </c>
-      <c r="E62" s="29" t="n">
+      <c r="E62" s="25" t="n">
         <v>807</v>
       </c>
-      <c r="F62" s="29" t="n">
+      <c r="F62" s="25" t="n">
         <v>3306</v>
       </c>
     </row>
@@ -1810,16 +1807,16 @@
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="C63" s="29" t="n">
+      <c r="C63" s="25" t="n">
         <v>4372</v>
       </c>
-      <c r="D63" s="29" t="n">
+      <c r="D63" s="25" t="n">
         <v>4430</v>
       </c>
-      <c r="E63" s="29" t="n">
+      <c r="E63" s="25" t="n">
         <v>5188</v>
       </c>
-      <c r="F63" s="29" t="n">
+      <c r="F63" s="25" t="n">
         <v>20832</v>
       </c>
     </row>
@@ -1829,16 +1826,16 @@
           <t>Net PPE</t>
         </is>
       </c>
-      <c r="C64" s="29" t="n">
+      <c r="C64" s="25" t="n">
         <v>4845</v>
       </c>
-      <c r="D64" s="29" t="n">
+      <c r="D64" s="25" t="n">
         <v>5260</v>
       </c>
-      <c r="E64" s="29" t="n">
+      <c r="E64" s="25" t="n">
         <v>8076</v>
       </c>
-      <c r="F64" s="29" t="n">
+      <c r="F64" s="25" t="n">
         <v>13250</v>
       </c>
     </row>
@@ -1848,16 +1845,16 @@
           <t>Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="C65" s="29" t="n">
+      <c r="C65" s="25" t="n">
         <v>-2694</v>
       </c>
-      <c r="D65" s="29" t="n">
+      <c r="D65" s="25" t="n">
         <v>-3509</v>
       </c>
-      <c r="E65" s="29" t="n">
+      <c r="E65" s="25" t="n">
         <v>-4401</v>
       </c>
-      <c r="F65" s="29" t="n">
+      <c r="F65" s="25" t="n">
         <v>-6587</v>
       </c>
     </row>
@@ -1867,16 +1864,16 @@
           <t>Gross PPE</t>
         </is>
       </c>
-      <c r="C66" s="29" t="n">
+      <c r="C66" s="25" t="n">
         <v>7539</v>
       </c>
-      <c r="D66" s="29" t="n">
+      <c r="D66" s="25" t="n">
         <v>8769</v>
       </c>
-      <c r="E66" s="29" t="n">
+      <c r="E66" s="25" t="n">
         <v>12477</v>
       </c>
-      <c r="F66" s="29" t="n">
+      <c r="F66" s="25" t="n">
         <v>19837</v>
       </c>
     </row>
@@ -1886,16 +1883,16 @@
           <t>Construction In Progress</t>
         </is>
       </c>
-      <c r="C67" s="29" t="n">
+      <c r="C67" s="25" t="n">
         <v>382</v>
       </c>
-      <c r="D67" s="29" t="n">
+      <c r="D67" s="25" t="n">
         <v>189</v>
       </c>
-      <c r="E67" s="29" t="n">
+      <c r="E67" s="25" t="n">
         <v>529</v>
       </c>
-      <c r="F67" s="29" t="n">
+      <c r="F67" s="25" t="n">
         <v>683</v>
       </c>
     </row>
@@ -1905,16 +1902,16 @@
           <t>Other Properties</t>
         </is>
       </c>
-      <c r="C68" s="29" t="n">
+      <c r="C68" s="25" t="n">
         <v>1038</v>
       </c>
-      <c r="D68" s="29" t="n">
+      <c r="D68" s="25" t="n">
         <v>1346</v>
       </c>
-      <c r="E68" s="29" t="n">
+      <c r="E68" s="25" t="n">
         <v>1793</v>
       </c>
-      <c r="F68" s="29" t="n">
+      <c r="F68" s="25" t="n">
         <v>2867</v>
       </c>
     </row>
@@ -1924,16 +1921,16 @@
           <t>Machinery Furniture Equipment</t>
         </is>
       </c>
-      <c r="C69" s="29" t="n">
+      <c r="C69" s="25" t="n">
         <v>4303</v>
       </c>
-      <c r="D69" s="29" t="n">
+      <c r="D69" s="25" t="n">
         <v>5200</v>
       </c>
-      <c r="E69" s="29" t="n">
+      <c r="E69" s="25" t="n">
         <v>7568</v>
       </c>
-      <c r="F69" s="29" t="n">
+      <c r="F69" s="25" t="n">
         <v>12619</v>
       </c>
     </row>
@@ -1943,16 +1940,16 @@
           <t>Buildings And Improvements</t>
         </is>
       </c>
-      <c r="C70" s="29" t="n">
+      <c r="C70" s="25" t="n">
         <v>1598</v>
       </c>
-      <c r="D70" s="29" t="n">
+      <c r="D70" s="25" t="n">
         <v>1816</v>
       </c>
-      <c r="E70" s="29" t="n">
+      <c r="E70" s="25" t="n">
         <v>2076</v>
       </c>
-      <c r="F70" s="29" t="n">
+      <c r="F70" s="25" t="n">
         <v>2891</v>
       </c>
     </row>
@@ -1962,16 +1959,16 @@
           <t>Land And Improvements</t>
         </is>
       </c>
-      <c r="C71" s="29" t="n">
+      <c r="C71" s="25" t="n">
         <v>218</v>
       </c>
-      <c r="D71" s="29" t="n">
+      <c r="D71" s="25" t="n">
         <v>218</v>
       </c>
-      <c r="E71" s="29" t="n">
+      <c r="E71" s="25" t="n">
         <v>511</v>
       </c>
-      <c r="F71" s="29" t="n">
+      <c r="F71" s="25" t="n">
         <v>777</v>
       </c>
     </row>
@@ -1981,16 +1978,16 @@
           <t>Properties</t>
         </is>
       </c>
-      <c r="C72" s="29" t="n">
+      <c r="C72" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D72" s="29" t="n">
+      <c r="D72" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="29" t="n">
+      <c r="E72" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F72" s="29" t="n">
+      <c r="F72" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2000,16 +1997,16 @@
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="C73" s="29" t="n">
+      <c r="C73" s="25" t="n">
         <v>23073</v>
       </c>
-      <c r="D73" s="29" t="n">
+      <c r="D73" s="25" t="n">
         <v>44345</v>
       </c>
-      <c r="E73" s="29" t="n">
+      <c r="E73" s="25" t="n">
         <v>80126</v>
       </c>
-      <c r="F73" s="29" t="n">
+      <c r="F73" s="25" t="n">
         <v>125605</v>
       </c>
     </row>
@@ -2019,16 +2016,16 @@
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="C74" s="29" t="n">
+      <c r="C74" s="25" t="n">
         <v>791</v>
       </c>
-      <c r="D74" s="29" t="n">
+      <c r="D74" s="25" t="n">
         <v>3080</v>
       </c>
-      <c r="E74" s="29" t="n">
+      <c r="E74" s="25" t="n">
         <v>3771</v>
       </c>
-      <c r="F74" s="29" t="n">
+      <c r="F74" s="25" t="n">
         <v>3180</v>
       </c>
     </row>
@@ -2038,7 +2035,7 @@
           <t>Prepaid Assets</t>
         </is>
       </c>
-      <c r="B75" s="29" t="n">
+      <c r="B75" s="25" t="n">
         <v>366</v>
       </c>
     </row>
@@ -2048,16 +2045,16 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C76" s="29" t="n">
+      <c r="C76" s="25" t="n">
         <v>5159</v>
       </c>
-      <c r="D76" s="29" t="n">
+      <c r="D76" s="25" t="n">
         <v>5282</v>
       </c>
-      <c r="E76" s="29" t="n">
+      <c r="E76" s="25" t="n">
         <v>10080</v>
       </c>
-      <c r="F76" s="29" t="n">
+      <c r="F76" s="25" t="n">
         <v>21403</v>
       </c>
     </row>
@@ -2067,16 +2064,16 @@
           <t>Finished Goods</t>
         </is>
       </c>
-      <c r="C77" s="29" t="n">
+      <c r="C77" s="25" t="n">
         <v>2263</v>
       </c>
-      <c r="D77" s="29" t="n">
+      <c r="D77" s="25" t="n">
         <v>2058</v>
       </c>
-      <c r="E77" s="29" t="n">
+      <c r="E77" s="25" t="n">
         <v>3273</v>
       </c>
-      <c r="F77" s="29" t="n">
+      <c r="F77" s="25" t="n">
         <v>8774</v>
       </c>
     </row>
@@ -2086,16 +2083,16 @@
           <t>Work In Process</t>
         </is>
       </c>
-      <c r="C78" s="29" t="n">
+      <c r="C78" s="25" t="n">
         <v>466</v>
       </c>
-      <c r="D78" s="29" t="n">
+      <c r="D78" s="25" t="n">
         <v>1505</v>
       </c>
-      <c r="E78" s="29" t="n">
+      <c r="E78" s="25" t="n">
         <v>3399</v>
       </c>
-      <c r="F78" s="29" t="n">
+      <c r="F78" s="25" t="n">
         <v>8822</v>
       </c>
     </row>
@@ -2105,16 +2102,16 @@
           <t>Raw Materials</t>
         </is>
       </c>
-      <c r="C79" s="29" t="n">
+      <c r="C79" s="25" t="n">
         <v>2430</v>
       </c>
-      <c r="D79" s="29" t="n">
+      <c r="D79" s="25" t="n">
         <v>1719</v>
       </c>
-      <c r="E79" s="29" t="n">
+      <c r="E79" s="25" t="n">
         <v>3408</v>
       </c>
-      <c r="F79" s="29" t="n">
+      <c r="F79" s="25" t="n">
         <v>3807</v>
       </c>
     </row>
@@ -2124,16 +2121,16 @@
           <t>Receivables</t>
         </is>
       </c>
-      <c r="C80" s="29" t="n">
+      <c r="C80" s="25" t="n">
         <v>3827</v>
       </c>
-      <c r="D80" s="29" t="n">
+      <c r="D80" s="25" t="n">
         <v>9999</v>
       </c>
-      <c r="E80" s="29" t="n">
+      <c r="E80" s="25" t="n">
         <v>23065</v>
       </c>
-      <c r="F80" s="29" t="n">
+      <c r="F80" s="25" t="n">
         <v>38466</v>
       </c>
     </row>
@@ -2143,16 +2140,16 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C81" s="29" t="n">
+      <c r="C81" s="25" t="n">
         <v>3827</v>
       </c>
-      <c r="D81" s="29" t="n">
+      <c r="D81" s="25" t="n">
         <v>9999</v>
       </c>
-      <c r="E81" s="29" t="n">
+      <c r="E81" s="25" t="n">
         <v>23065</v>
       </c>
-      <c r="F81" s="29" t="n">
+      <c r="F81" s="25" t="n">
         <v>38466</v>
       </c>
     </row>
@@ -2162,16 +2159,16 @@
           <t>Cash Cash Equivalents And Short Term Investments</t>
         </is>
       </c>
-      <c r="C82" s="29" t="n">
+      <c r="C82" s="25" t="n">
         <v>13296</v>
       </c>
-      <c r="D82" s="29" t="n">
+      <c r="D82" s="25" t="n">
         <v>25984</v>
       </c>
-      <c r="E82" s="29" t="n">
+      <c r="E82" s="25" t="n">
         <v>43210</v>
       </c>
-      <c r="F82" s="29" t="n">
+      <c r="F82" s="25" t="n">
         <v>62556</v>
       </c>
     </row>
@@ -2181,16 +2178,16 @@
           <t>Other Short Term Investments</t>
         </is>
       </c>
-      <c r="C83" s="29" t="n">
+      <c r="C83" s="25" t="n">
         <v>9907</v>
       </c>
-      <c r="D83" s="29" t="n">
+      <c r="D83" s="25" t="n">
         <v>18704</v>
       </c>
-      <c r="E83" s="29" t="n">
+      <c r="E83" s="25" t="n">
         <v>34621</v>
       </c>
-      <c r="F83" s="29" t="n">
+      <c r="F83" s="25" t="n">
         <v>51951</v>
       </c>
     </row>
@@ -2200,16 +2197,16 @@
           <t>Cash And Cash Equivalents</t>
         </is>
       </c>
-      <c r="C84" s="29" t="n">
+      <c r="C84" s="25" t="n">
         <v>3389</v>
       </c>
-      <c r="D84" s="29" t="n">
+      <c r="D84" s="25" t="n">
         <v>7280</v>
       </c>
-      <c r="E84" s="29" t="n">
+      <c r="E84" s="25" t="n">
         <v>8589</v>
       </c>
-      <c r="F84" s="29" t="n">
+      <c r="F84" s="25" t="n">
         <v>10605</v>
       </c>
     </row>
@@ -2245,7 +2242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-08 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -2287,16 +2284,16 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>3808</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>27021</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>60853</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>96676</v>
       </c>
     </row>
@@ -2306,16 +2303,16 @@
           <t>Repurchase Of Capital Stock</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="25" t="n">
         <v>-10039</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="25" t="n">
         <v>-9533</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="25" t="n">
         <v>-33706</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="25" t="n">
         <v>-40086</v>
       </c>
     </row>
@@ -2325,16 +2322,16 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>-1250</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>-1250</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2344,13 +2341,13 @@
           <t>Issuance Of Debt</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="25" t="n">
         <v>4977</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2360,16 +2357,16 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>-1833</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>-1069</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>-3236</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>-6042</v>
       </c>
     </row>
@@ -2379,16 +2376,16 @@
           <t>Interest Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="25" t="n">
         <v>246</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>254</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>252</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>246</v>
       </c>
     </row>
@@ -2398,16 +2395,16 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>1404</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>6549</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>15118</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>20288</v>
       </c>
     </row>
@@ -2417,16 +2414,16 @@
           <t>End Cash Position</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>3389</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>7280</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>8589</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>10605</v>
       </c>
     </row>
@@ -2436,16 +2433,16 @@
           <t>Beginning Cash Position</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>1990</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>3389</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>7280</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>8589</v>
       </c>
     </row>
@@ -2455,16 +2452,16 @@
           <t>Changes In Cash</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>1399</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>3891</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>1309</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>2016</v>
       </c>
     </row>
@@ -2474,16 +2471,16 @@
           <t>Financing Cash Flow</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>-11617</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>-13633</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>-42359</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>-48474</v>
       </c>
     </row>
@@ -2493,16 +2490,16 @@
           <t>Cash Flow From Continuing Financing Activities</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>-11617</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>-13633</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>-42359</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>-48474</v>
       </c>
     </row>
@@ -2512,16 +2509,16 @@
           <t>Net Other Financing Charges</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>-1535</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>-2858</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>-7059</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>-8058</v>
       </c>
     </row>
@@ -2531,16 +2528,16 @@
           <t>Proceeds From Stock Option Exercised</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>355</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>403</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>490</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>644</v>
       </c>
     </row>
@@ -2550,16 +2547,16 @@
           <t>Cash Dividends Paid</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>-398</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>-395</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>-834</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>-974</v>
       </c>
     </row>
@@ -2569,16 +2566,16 @@
           <t>Common Stock Dividend Paid</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>-398</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>-395</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>-834</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>-974</v>
       </c>
     </row>
@@ -2588,16 +2585,16 @@
           <t>Net Common Stock Issuance</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>-10039</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>-9533</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>-33706</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>-40086</v>
       </c>
     </row>
@@ -2607,16 +2604,16 @@
           <t>Common Stock Payments</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>-10039</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>-9533</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>-33706</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>-40086</v>
       </c>
     </row>
@@ -2626,16 +2623,16 @@
           <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>-1250</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>-1250</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2645,16 +2642,16 @@
           <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="25" t="n">
         <v>-1250</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="25" t="n">
         <v>-1250</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2664,16 +2661,16 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="25" t="n">
         <v>-1250</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="25" t="n">
         <v>-1250</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2683,13 +2680,13 @@
           <t>Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="25" t="n">
         <v>4977</v>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2699,16 +2696,16 @@
           <t>Investing Cash Flow</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>7375</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>-10566</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>-20421</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>-52228</v>
       </c>
     </row>
@@ -2718,16 +2715,16 @@
           <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>7375</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>-10566</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>-20421</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>-52228</v>
       </c>
     </row>
@@ -2737,10 +2734,10 @@
           <t>Net Other Investing Changes</t>
         </is>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>-124</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>22</v>
       </c>
     </row>
@@ -2750,16 +2747,16 @@
           <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>9257</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>-9290</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="25" t="n">
         <v>-16200</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="25" t="n">
         <v>-31651</v>
       </c>
     </row>
@@ -2769,16 +2766,16 @@
           <t>Sale Of Investment</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>21239</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>9783</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>11861</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>26467</v>
       </c>
     </row>
@@ -2788,16 +2785,16 @@
           <t>Purchase Of Investment</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>-11982</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>-19073</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>-28061</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>-58118</v>
       </c>
     </row>
@@ -2807,16 +2804,16 @@
           <t>Net Business Purchase And Sale</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>-49</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>-83</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>-1007</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>-14535</v>
       </c>
     </row>
@@ -2826,16 +2823,16 @@
           <t>Purchase Of Business</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>-49</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>-83</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>-1007</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>-14535</v>
       </c>
     </row>
@@ -2845,16 +2842,16 @@
           <t>Net PPE Purchase And Sale</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>-1833</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>-1069</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>-3236</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="25" t="n">
         <v>-6042</v>
       </c>
     </row>
@@ -2864,16 +2861,16 @@
           <t>Purchase Of PPE</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>-1833</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>-1069</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <v>-3236</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="25" t="n">
         <v>-6042</v>
       </c>
     </row>
@@ -2883,16 +2880,16 @@
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>5641</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>28090</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>64089</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>102718</v>
       </c>
     </row>
@@ -2902,16 +2899,16 @@
           <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>5640</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>28090</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>64089</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>102718</v>
       </c>
     </row>
@@ -2921,16 +2918,16 @@
           <t>Change In Working Capital</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>-2207</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>-3722</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>-9383</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="25" t="n">
         <v>-15949</v>
       </c>
     </row>
@@ -2940,16 +2937,16 @@
           <t>Change In Other Current Liabilities</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>252</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>514</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="25" t="n">
         <v>1221</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>1844</v>
       </c>
     </row>
@@ -2959,16 +2956,16 @@
           <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>790</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>3556</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>7635</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>8353</v>
       </c>
     </row>
@@ -2978,16 +2975,16 @@
           <t>Change In Accrued Expense</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>1341</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>2025</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="25" t="n">
         <v>4278</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="25" t="n">
         <v>5257</v>
       </c>
     </row>
@@ -2997,16 +2994,16 @@
           <t>Change In Payable</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>-551</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>1531</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="25" t="n">
         <v>3357</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>3096</v>
       </c>
     </row>
@@ -3016,16 +3013,16 @@
           <t>Change In Account Payable</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>-551</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>1531</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>3357</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>3096</v>
       </c>
     </row>
@@ -3035,16 +3032,16 @@
           <t>Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>-1517</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>-1522</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>-395</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>577</v>
       </c>
     </row>
@@ -3054,16 +3051,16 @@
           <t>Change In Inventory</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>-2554</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>-98</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>-4781</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>-11324</v>
       </c>
     </row>
@@ -3073,16 +3070,16 @@
           <t>Change In Receivables</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>822</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>-6172</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="25" t="n">
         <v>-13063</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="25" t="n">
         <v>-15399</v>
       </c>
     </row>
@@ -3092,16 +3089,16 @@
           <t>Changes In Account Receivables</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>822</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>-6172</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>-13063</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>-15399</v>
       </c>
     </row>
@@ -3111,16 +3108,16 @@
           <t>Other Non Cash Items</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>1347</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>-278</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>-502</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>-287</v>
       </c>
     </row>
@@ -3130,16 +3127,16 @@
           <t>Stock Based Compensation</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>2709</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>3549</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="25" t="n">
         <v>4737</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="25" t="n">
         <v>6386</v>
       </c>
     </row>
@@ -3149,16 +3146,16 @@
           <t>Deferred Tax</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>-2164</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>-2489</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>-4477</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>-1424</v>
       </c>
     </row>
@@ -3168,16 +3165,16 @@
           <t>Deferred Income Tax</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>-2164</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>-2489</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>-4477</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>-1424</v>
       </c>
     </row>
@@ -3187,16 +3184,16 @@
           <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>1543</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="25" t="n">
         <v>1508</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="25" t="n">
         <v>1864</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="25" t="n">
         <v>2843</v>
       </c>
     </row>
@@ -3206,16 +3203,16 @@
           <t>Depreciation And Amortization</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>1543</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>1508</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>1864</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="25" t="n">
         <v>2843</v>
       </c>
     </row>
@@ -3225,13 +3222,13 @@
           <t>Amortization Cash Flow</t>
         </is>
       </c>
-      <c r="B55" s="29" t="n">
+      <c r="B55" s="25" t="n">
         <v>563</v>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>699</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>614</v>
       </c>
     </row>
@@ -3241,13 +3238,13 @@
           <t>Amortization Of Intangibles</t>
         </is>
       </c>
-      <c r="B56" s="29" t="n">
+      <c r="B56" s="25" t="n">
         <v>563</v>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>699</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="25" t="n">
         <v>614</v>
       </c>
     </row>
@@ -3257,13 +3254,13 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="29" t="n">
+      <c r="B57" s="25" t="n">
         <v>611</v>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="25" t="n">
         <v>844</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="25" t="n">
         <v>894</v>
       </c>
     </row>
@@ -3273,16 +3270,16 @@
           <t>Operating Gains Losses</t>
         </is>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="25" t="n">
         <v>45</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="25" t="n">
         <v>-238</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="25" t="n">
         <v>-1030</v>
       </c>
-      <c r="F58" s="29" t="n">
+      <c r="F58" s="25" t="n">
         <v>-8918</v>
       </c>
     </row>
@@ -3292,16 +3289,16 @@
           <t>Gain Loss On Investment Securities</t>
         </is>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="25" t="n">
         <v>45</v>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="25" t="n">
         <v>-238</v>
       </c>
-      <c r="E59" s="29" t="n">
+      <c r="E59" s="25" t="n">
         <v>-1030</v>
       </c>
-      <c r="F59" s="29" t="n">
+      <c r="F59" s="25" t="n">
         <v>-8918</v>
       </c>
     </row>
@@ -3311,16 +3308,16 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="C60" s="29" t="n">
+      <c r="C60" s="25" t="n">
         <v>4368</v>
       </c>
-      <c r="D60" s="29" t="n">
+      <c r="D60" s="25" t="n">
         <v>29760</v>
       </c>
-      <c r="E60" s="29" t="n">
+      <c r="E60" s="25" t="n">
         <v>72880</v>
       </c>
-      <c r="F60" s="29" t="n">
+      <c r="F60" s="25" t="n">
         <v>120067</v>
       </c>
     </row>
@@ -3330,6 +3327,285 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NVDA — 12-month price target (lens triangulation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Blue = inputs (weights, Ke, dividends, Street weight); black = live formulas. Change a weight and the blended fair value and target recalculate. Guardrail exclusions are already reflected in the effective weights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Value / share</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Discounted cash flow (FCFF)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>intrinsic</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>197.12664298595</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>176.7483467801727</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>219.4191710831196</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Forward P/E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>283.200225</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>232.2241845</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>334.1762654999999</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Forward EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>239.7677707994089</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>196.992416694465</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>282.5431249043529</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Weights sum</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>SUM(F5:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Blended fair value (today)</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>SUMPRODUCT(C5:C7,F5:F7)/SUM(F5:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cost of equity (Ke)</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>0.1146038799367739</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Dividends per share (12m)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>0.0402</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Model 12-month target = FV×(1+Ke)−DPS</t>
+        </is>
+      </c>
+      <c r="B13" s="16">
+        <f>$B$10*(1+$B$11)-$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Street mean target</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>301.62</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Street weight in target</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Published 12-month target</t>
+        </is>
+      </c>
+      <c r="B16" s="17">
+        <f>(1-$B$15)*$B$13+$B$15*$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>204.12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Engine target (incl. plausibility band)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>270.3735326589133</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Guardrails</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Target anchored 15% to the Street consensus ($301.62); model-only target $264.86.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3354,14 +3630,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NVDA — projected P&amp;L &amp; levered FCF (analyst-driven)</t>
+          <t>NVDA — projected P&amp;L &amp; levered FCF (DCF base case)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue = analyst estimates; black = live formulas. The Levered FCF row is the exact cash flow discounted on the 'SWS Valuation' sheet — P&amp;L, cash flow and fair value are one reconciled chain.</t>
+          <t>Blue = consensus-sourced figures; black = live formulas. Revenue and EBIT margin are the DCF base-case drivers; levered FCF = unlevered FCF less after-tax interest.</t>
         </is>
       </c>
     </row>
@@ -3423,40 +3699,40 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Revenue (mn)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>554435.30715</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>571068.3663645</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>588200.4173554351</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>605846.4298760982</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>624021.8227723811</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>642742.4774555527</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>662024.7517792193</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>681885.4943325958</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>702342.0591625738</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>723412.320937451</v>
+      <c r="B5" s="18" t="n">
+        <v>554440</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>645806.0994400255</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>726668.3413311919</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>797037.8965057848</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>858010.523282606</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>911136.9650182693</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>958029.1498762461</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>1000155.99589244</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>1038762.787695176</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>1064731.857387555</v>
       </c>
     </row>
     <row r="6">
@@ -3470,39 +3746,39 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="12">
         <f>J5/I5-1</f>
         <v/>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="12">
         <f>K5/J5-1</f>
         <v/>
       </c>
@@ -3513,35 +3789,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
-        <v>0.6038168363141272</v>
-      </c>
-      <c r="C7" s="15" t="n">
-        <v>0.6038168363141272</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>0.6038168363141272</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.6038168363141272</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0.6038168363141272</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.6038168363141272</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.6038168363141272</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>0.6038168363141272</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>0.6038168363141272</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.6038168363141272</v>
+      <c r="B7" s="11" t="n">
+        <v>0.6445974830850275</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>0.638142913042177</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0.6316883429993265</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.625233772956476</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.6187792029136255</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>0.612324632870775</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0.6058700628279245</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0.599415492785074</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>0.599415492785074</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0.599415492785074</v>
       </c>
     </row>
     <row r="8">
@@ -3550,43 +3826,43 @@
           <t>EBIT (mn)</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="19">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="19">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="19">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="19">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="19">
         <f>F5*F7</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="19">
         <f>G5*G7</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="19">
         <f>H5*H7</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="19">
         <f>I5*I7</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="19">
         <f>J5*J7</f>
         <v/>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="19">
         <f>K5*K7</f>
         <v/>
       </c>
@@ -3597,35 +3873,35 @@
           <t>Net income (mn)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>309167.25903</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>317528.4829177191</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>327054.3374052508</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>336865.9675274083</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>346971.9465532305</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>357381.1049498275</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>368102.5380983223</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>379145.614241272</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>390519.9826685101</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>402235.5821485654</v>
+      <c r="B9" s="18" t="n">
+        <v>309059.96</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>356419.5348501363</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>397016.3740161437</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>431032.5376173494</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>459230.6202960665</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>482589.8319678983</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>502086.8145026244</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>518588.0106189381</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>538614.5591402202</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>552085.5265519732</v>
       </c>
     </row>
     <row r="10">
@@ -3676,40 +3952,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Levered FCF (mn)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>269530.4309492308</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>278963.9960324538</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>288727.7358935897</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>298833.2066498654</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>309292.3688826106</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>320117.6017935019</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>331321.7178562745</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>342917.9779812441</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>354920.1072105876</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>367342.3109629581</v>
+      <c r="B12" s="20" t="n">
+        <v>256407.5697703674</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>338948.2586116076</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>380873.3017311503</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>416356.6828550179</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>445983.7109139795</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>470646.8302946997</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>491295.3462942344</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>508801.4578386336</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>529707.2972319083</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>545440.9956541875</v>
       </c>
     </row>
     <row r="13">
@@ -3718,43 +3994,43 @@
           <t>FCF margin</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="12">
         <f>B12/B5</f>
         <v/>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="12">
         <f>C12/C5</f>
         <v/>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="12">
         <f>D12/D5</f>
         <v/>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <f>E12/E5</f>
         <v/>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <f>F12/F5</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="12">
         <f>G12/G5</f>
         <v/>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="12">
         <f>H12/H5</f>
         <v/>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="12">
         <f>I12/I5</f>
         <v/>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="12">
         <f>J12/J5</f>
         <v/>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="12">
         <f>K12/K5</f>
         <v/>
       </c>
@@ -3762,438 +4038,8 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>→ These Levered FCF figures feed the DCF on the 'SWS Valuation' sheet.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>NVDA — 2-Stage Free Cash Flow to Equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Simply Wall St methodology. Blue = analyst inputs you can change; black = live formulas. Discounted at the cost of equity. Every figure is traceable; change a blue cell and the model recalculates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Cost of equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Risk-free rate</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>0.036</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Equity risk premium</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>0.046</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Levered beta (clamped 0.8–2.0)</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>1.202</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Cost of equity = Rf + β·ERP</t>
-        </is>
-      </c>
-      <c r="B8" s="20">
-        <f>$B$5+$B$7*$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Perpetual growth (g)</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>24221</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Stage 1 — 10-year cash-flow forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Cash flow (mn)</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>PV (mn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>269530.4309492308</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D15" s="22">
-        <f>1/(1+$B$8)^1</f>
-        <v/>
-      </c>
-      <c r="E15" s="13">
-        <f>B15*D15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>278963.9960324538</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D16" s="22">
-        <f>1/(1+$B$8)^2</f>
-        <v/>
-      </c>
-      <c r="E16" s="13">
-        <f>B16*D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>2029</v>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>288727.7358935897</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D17" s="22">
-        <f>1/(1+$B$8)^3</f>
-        <v/>
-      </c>
-      <c r="E17" s="13">
-        <f>B17*D17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>298833.2066498654</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D18" s="22">
-        <f>1/(1+$B$8)^4</f>
-        <v/>
-      </c>
-      <c r="E18" s="13">
-        <f>B18*D18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>2031</v>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>309292.3688826106</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D19" s="22">
-        <f>1/(1+$B$8)^5</f>
-        <v/>
-      </c>
-      <c r="E19" s="13">
-        <f>B19*D19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
-        <v>2032</v>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>320117.6017935019</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D20" s="22">
-        <f>1/(1+$B$8)^6</f>
-        <v/>
-      </c>
-      <c r="E20" s="13">
-        <f>B20*D20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n">
-        <v>2033</v>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>331321.7178562745</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D21" s="22">
-        <f>1/(1+$B$8)^7</f>
-        <v/>
-      </c>
-      <c r="E21" s="13">
-        <f>B21*D21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>342917.9779812441</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D22" s="22">
-        <f>1/(1+$B$8)^8</f>
-        <v/>
-      </c>
-      <c r="E22" s="13">
-        <f>B22*D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>354920.1072105876</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D23" s="22">
-        <f>1/(1+$B$8)^9</f>
-        <v/>
-      </c>
-      <c r="E23" s="13">
-        <f>B23*D23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="n">
-        <v>2036</v>
-      </c>
-      <c r="B24" s="12" t="n">
-        <v>367342.3109629581</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D24" s="22">
-        <f>1/(1+$B$8)^10</f>
-        <v/>
-      </c>
-      <c r="E24" s="13">
-        <f>B24*D24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>PV of next 10 years' cash flows</t>
-        </is>
-      </c>
-      <c r="B25" s="23">
-        <f>SUM(E15:E24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Stage 2 — terminal value</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Terminal value = CFn·(1+g)/(Ke−g)</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <f>B24*(1+$B$10)/($B$8-$B$10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="B29" s="13">
-        <f>$B$28/(1+$B$8)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Total equity value</t>
-        </is>
-      </c>
-      <c r="B31" s="23">
-        <f>$B$25+$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Value per share</t>
-        </is>
-      </c>
-      <c r="B32" s="24">
-        <f>$B$31/$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Current price</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>204.12</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Upside / (downside)</t>
-        </is>
-      </c>
-      <c r="B34" s="14">
-        <f>B32/$B$33-1</f>
-        <v/>
+          <t>→ Unlevered FCF (before interest) is what the 'DCF' sheet discounts.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4207,7 +4053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4233,7 +4079,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue cells are inputs — change them and the whole model recalculates. Source: yfinance, retrieved 2026-07-08.</t>
+          <t>Blue cells are inputs — change them and the whole model recalculates. Source: Yahoo snapshot as of 2026-07-08, retrieved 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4106,7 @@
           <t>Diluted shares (mn)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="18" t="n">
         <v>24221</v>
       </c>
     </row>
@@ -4270,7 +4116,7 @@
           <t>Total debt (USDmm)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="18" t="n">
         <v>11040</v>
       </c>
     </row>
@@ -4280,7 +4126,7 @@
           <t>Cash &amp; ST investments (USDmm)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="18" t="n">
         <v>62556</v>
       </c>
     </row>
@@ -4290,7 +4136,7 @@
           <t>Minority interest (USDmm)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4300,7 +4146,7 @@
           <t>Net debt (USDmm)</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="19">
         <f>Assumptions!$B$7-Assumptions!$B$8</f>
         <v/>
       </c>
@@ -4318,7 +4164,7 @@
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="21" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -4328,7 +4174,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="21" t="n">
         <v>0.046</v>
       </c>
     </row>
@@ -4338,7 +4184,7 @@
           <t>Country risk premium</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4348,7 +4194,7 @@
           <t>Size premium</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4358,8 +4204,8 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
-        <v>2.21</v>
+      <c r="B17" s="22" t="n">
+        <v>1.56</v>
       </c>
     </row>
     <row r="18">
@@ -4368,7 +4214,7 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="15" t="n">
         <v>0.04899999999999999</v>
       </c>
     </row>
@@ -4378,7 +4224,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="11" t="n">
         <v>0.1346049038575892</v>
       </c>
     </row>
@@ -4395,7 +4241,7 @@
           <t>Terminal growth (g)</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="21" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -4437,6 +4283,31 @@
           <t>FY2031E</t>
         </is>
       </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>FY2036E</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -4444,20 +4315,35 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C26" s="15" t="n">
-        <v>0.19375</v>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>0.1375</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0.08124999999999999</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>0.02499999999999999</v>
+      <c r="B26" s="11" t="n">
+        <v>1.567588844946235</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>0.1647898770651929</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>0.125211331948214</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0.09683861422348755</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>0.07649903102992379</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>0.06191817034179282</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>0.05146557176180035</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>0.04397240524636979</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>0.03860077024113361</v>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="27">
@@ -4466,20 +4352,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v>0.6038168363141272</v>
-      </c>
-      <c r="C27" s="15" t="n">
-        <v>0.5928342375578994</v>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>0.5818516388016716</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.5708690400454437</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>0.5598864412892159</v>
+      <c r="B27" s="11" t="n">
+        <v>0.6445974830850275</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0.638142913042177</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0.6316883429993265</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0.625233772956476</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0.6187792029136255</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>0.612324632870775</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>0.6058700628279245</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>0.599415492785074</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>0.599415492785074</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>0.599415492785074</v>
       </c>
     </row>
     <row r="28">
@@ -4488,19 +4389,34 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
+      <c r="B28" s="11" t="n">
         <v>0.0273514662325203</v>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C28" s="11" t="n">
         <v>0.0273514662325203</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="11" t="n">
         <v>0.0273514662325203</v>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="E28" s="11" t="n">
         <v>0.0273514662325203</v>
       </c>
-      <c r="F28" s="15" t="n">
+      <c r="F28" s="11" t="n">
+        <v>0.0273514662325203</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>0.0273514662325203</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>0.0273514662325203</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0.0273514662325203</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>0.0273514662325203</v>
+      </c>
+      <c r="K28" s="11" t="n">
         <v>0.0273514662325203</v>
       </c>
     </row>
@@ -4510,20 +4426,35 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n">
+      <c r="B29" s="11" t="n">
         <v>0.03456977806240261</v>
       </c>
-      <c r="C29" s="15" t="n">
-        <v>0.03456977806240261</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>0.03456977806240261</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.03456977806240261</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0.03456977806240261</v>
+      <c r="C29" s="11" t="n">
+        <v>0.03407164859499924</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.03357351912759587</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0.03307538966019252</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0.03257726019278915</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0.03207913072538578</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>0.03158100125798242</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>0.03108287179057906</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>0.03058474232317569</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>0.03008661285577233</v>
       </c>
     </row>
     <row r="30">
@@ -4532,7 +4463,7 @@
           <t>ΔNWC % of Δrevenue</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
+      <c r="B30" s="11" t="n">
         <v>0.1437222510315231</v>
       </c>
     </row>
@@ -4596,7 +4527,7 @@
           <t>Market value of equity (mm)</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="23">
         <f>Assumptions!$B$5*Assumptions!$B$6</f>
         <v/>
       </c>
@@ -4607,7 +4538,7 @@
           <t>Debt (book, mm)</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="23">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
@@ -4618,7 +4549,7 @@
           <t>Weight of equity</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="12">
         <f>WACC!$B$6/(WACC!$B$6+WACC!$B$7)</f>
         <v/>
       </c>
@@ -4629,18 +4560,18 @@
           <t>Weight of debt</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="12">
         <f>1-WACC!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="24">
         <f>WACC!$B$8*WACC!$B$4+WACC!$B$9*WACC!$B$5</f>
         <v/>
       </c>
@@ -4656,7 +4587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4669,6 +4600,11 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4736,6 +4672,31 @@
           <t>FY2031E</t>
         </is>
       </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>FY2036E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4743,36 +4704,56 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="25" t="n">
         <v>26974</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>60922</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>130497</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>215938</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="19">
         <f>E5*(1+Assumptions!B$26)</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="19">
         <f>F5*(1+Assumptions!C$26)</f>
         <v/>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="19">
         <f>G5*(1+Assumptions!D$26)</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="19">
         <f>H5*(1+Assumptions!E$26)</f>
         <v/>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="19">
         <f>I5*(1+Assumptions!F$26)</f>
+        <v/>
+      </c>
+      <c r="K5" s="19">
+        <f>J5*(1+Assumptions!G$26)</f>
+        <v/>
+      </c>
+      <c r="L5" s="19">
+        <f>K5*(1+Assumptions!H$26)</f>
+        <v/>
+      </c>
+      <c r="M5" s="19">
+        <f>L5*(1+Assumptions!I$26)</f>
+        <v/>
+      </c>
+      <c r="N5" s="19">
+        <f>M5*(1+Assumptions!J$26)</f>
+        <v/>
+      </c>
+      <c r="O5" s="19">
+        <f>N5*(1+Assumptions!K$26)</f>
         <v/>
       </c>
     </row>
@@ -4782,36 +4763,56 @@
           <t xml:space="preserve">  growth %</t>
         </is>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="26">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="26">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="26">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="12">
         <f>J5/I5-1</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>K5/J5-1</f>
+        <v/>
+      </c>
+      <c r="L6" s="12">
+        <f>L5/K5-1</f>
+        <v/>
+      </c>
+      <c r="M6" s="12">
+        <f>M5/L5-1</f>
+        <v/>
+      </c>
+      <c r="N6" s="12">
+        <f>N5/M5-1</f>
+        <v/>
+      </c>
+      <c r="O6" s="12">
+        <f>O5/N5-1</f>
         <v/>
       </c>
     </row>
@@ -4821,36 +4822,56 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <v>5577</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>32972</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>81453</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>130387</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="19">
         <f>F5*Assumptions!B$27</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="19">
         <f>G5*Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="19">
         <f>H5*Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="19">
         <f>I5*Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="19">
         <f>J5*Assumptions!F$27</f>
+        <v/>
+      </c>
+      <c r="K7" s="19">
+        <f>K5*Assumptions!G$27</f>
+        <v/>
+      </c>
+      <c r="L7" s="19">
+        <f>L5*Assumptions!H$27</f>
+        <v/>
+      </c>
+      <c r="M7" s="19">
+        <f>M5*Assumptions!I$27</f>
+        <v/>
+      </c>
+      <c r="N7" s="19">
+        <f>N5*Assumptions!J$27</f>
+        <v/>
+      </c>
+      <c r="O7" s="19">
+        <f>O5*Assumptions!K$27</f>
         <v/>
       </c>
     </row>
@@ -4860,40 +4881,60 @@
           <t xml:space="preserve">  EBIT margin %</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="26">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="26">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="26">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="26">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="12">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="12">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="12">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="12">
         <f>I7/I5</f>
         <v/>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="12">
         <f>J7/J5</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>K7/K5</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>L7/L5</f>
+        <v/>
+      </c>
+      <c r="M8" s="12">
+        <f>M7/M5</f>
+        <v/>
+      </c>
+      <c r="N8" s="12">
+        <f>N7/N5</f>
+        <v/>
+      </c>
+      <c r="O8" s="12">
+        <f>O7/O5</f>
         <v/>
       </c>
     </row>
@@ -4903,36 +4944,56 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="25" t="n">
         <v>1543</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>1508</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>1864</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>2843</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="19">
         <f>F5*Assumptions!B$28</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="19">
         <f>G5*Assumptions!C$28</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="19">
         <f>H5*Assumptions!D$28</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="19">
         <f>I5*Assumptions!E$28</f>
         <v/>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="19">
         <f>J5*Assumptions!F$28</f>
+        <v/>
+      </c>
+      <c r="K9" s="19">
+        <f>K5*Assumptions!G$28</f>
+        <v/>
+      </c>
+      <c r="L9" s="19">
+        <f>L5*Assumptions!H$28</f>
+        <v/>
+      </c>
+      <c r="M9" s="19">
+        <f>M5*Assumptions!I$28</f>
+        <v/>
+      </c>
+      <c r="N9" s="19">
+        <f>N5*Assumptions!J$28</f>
+        <v/>
+      </c>
+      <c r="O9" s="19">
+        <f>O5*Assumptions!K$28</f>
         <v/>
       </c>
     </row>
@@ -4942,40 +5003,60 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="27">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="27">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="27">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="27">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="19">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="19">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="19">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="19">
         <f>I7+I9</f>
         <v/>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="19">
         <f>J7+J9</f>
+        <v/>
+      </c>
+      <c r="K10" s="19">
+        <f>K7+K9</f>
+        <v/>
+      </c>
+      <c r="L10" s="19">
+        <f>L7+L9</f>
+        <v/>
+      </c>
+      <c r="M10" s="19">
+        <f>M7+M9</f>
+        <v/>
+      </c>
+      <c r="N10" s="19">
+        <f>N7+N9</f>
+        <v/>
+      </c>
+      <c r="O10" s="19">
+        <f>O7+O9</f>
         <v/>
       </c>
     </row>
@@ -4985,40 +5066,60 @@
           <t>NOPAT (EBIT×(1−t))</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="28">
         <f>B7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="28">
         <f>C7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="28">
         <f>D7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="28">
         <f>E7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="23">
         <f>F7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="23">
         <f>G7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="23">
         <f>H7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="23">
         <f>I7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="23">
         <f>J7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="K11" s="23">
+        <f>K7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="L11" s="23">
+        <f>L7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="M11" s="23">
+        <f>M7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="N11" s="23">
+        <f>N7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="O11" s="23">
+        <f>O7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -5028,36 +5129,56 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="25" t="n">
         <v>1833</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>1069</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>3236</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>6042</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="19">
         <f>F5*Assumptions!B$29</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="19">
         <f>G5*Assumptions!C$29</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="19">
         <f>H5*Assumptions!D$29</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="19">
         <f>I5*Assumptions!E$29</f>
         <v/>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="19">
         <f>J5*Assumptions!F$29</f>
+        <v/>
+      </c>
+      <c r="K12" s="19">
+        <f>K5*Assumptions!G$29</f>
+        <v/>
+      </c>
+      <c r="L12" s="19">
+        <f>L5*Assumptions!H$29</f>
+        <v/>
+      </c>
+      <c r="M12" s="19">
+        <f>M5*Assumptions!I$29</f>
+        <v/>
+      </c>
+      <c r="N12" s="19">
+        <f>N5*Assumptions!J$29</f>
+        <v/>
+      </c>
+      <c r="O12" s="19">
+        <f>O5*Assumptions!K$29</f>
         <v/>
       </c>
     </row>
@@ -5067,79 +5188,119 @@
           <t>Δ Net working capital</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="25" t="n">
         <v>2207</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>3722</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>9383</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>15949</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="19">
         <f>(F5-E5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="19">
         <f>(G5-F5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="19">
         <f>(H5-G5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="19">
         <f>(I5-H5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="19">
         <f>(J5-I5)*Assumptions!$B$30</f>
         <v/>
       </c>
+      <c r="K13" s="19">
+        <f>(K5-J5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="L13" s="19">
+        <f>(L5-K5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="M13" s="19">
+        <f>(M5-L5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="N13" s="19">
+        <f>(N5-M5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="O13" s="19">
+        <f>(O5-N5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="29">
         <f>B11+B9-B12-B13</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="29">
         <f>C11+C9-C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="29">
         <f>D11+D9-D12-D13</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="29">
         <f>E11+E9-E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="30">
         <f>F11+F9-F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="30">
         <f>G11+G9-G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="30">
         <f>H11+H9-H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="30">
         <f>I11+I9-I12-I13</f>
         <v/>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="30">
         <f>J11+J9-J12-J13</f>
+        <v/>
+      </c>
+      <c r="K14" s="30">
+        <f>K11+K9-K12-K13</f>
+        <v/>
+      </c>
+      <c r="L14" s="30">
+        <f>L11+L9-L12-L13</f>
+        <v/>
+      </c>
+      <c r="M14" s="30">
+        <f>M11+M9-M12-M13</f>
+        <v/>
+      </c>
+      <c r="N14" s="30">
+        <f>N11+N9-N12-N13</f>
+        <v/>
+      </c>
+      <c r="O14" s="30">
+        <f>O11+O9-O12-O13</f>
         <v/>
       </c>
     </row>
@@ -5154,7 +5315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5164,6 +5325,11 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5211,6 +5377,31 @@
           <t>FY2031E</t>
         </is>
       </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2036E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5218,24 +5409,44 @@
           <t>FCFF (from Model)</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="23">
         <f>Model!F14</f>
         <v/>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="23">
         <f>Model!G14</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="23">
         <f>Model!H14</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="23">
         <f>Model!I14</f>
         <v/>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="23">
         <f>Model!J14</f>
+        <v/>
+      </c>
+      <c r="G5" s="23">
+        <f>Model!K14</f>
+        <v/>
+      </c>
+      <c r="H5" s="23">
+        <f>Model!L14</f>
+        <v/>
+      </c>
+      <c r="I5" s="23">
+        <f>Model!M14</f>
+        <v/>
+      </c>
+      <c r="J5" s="23">
+        <f>Model!N14</f>
+        <v/>
+      </c>
+      <c r="K5" s="23">
+        <f>Model!O14</f>
         <v/>
       </c>
     </row>
@@ -5245,20 +5456,35 @@
           <t>Period (mid-year, t−0.5)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="31" t="n">
         <v>3.5</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="31" t="n">
         <v>4.5</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
@@ -5267,24 +5493,44 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="32">
         <f>1/(1+WACC!$B$10)^B6</f>
         <v/>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="32">
         <f>1/(1+WACC!$B$10)^C6</f>
         <v/>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="32">
         <f>1/(1+WACC!$B$10)^D6</f>
         <v/>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="32">
         <f>1/(1+WACC!$B$10)^E6</f>
         <v/>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="32">
         <f>1/(1+WACC!$B$10)^F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="32">
+        <f>1/(1+WACC!$B$10)^G6</f>
+        <v/>
+      </c>
+      <c r="H7" s="32">
+        <f>1/(1+WACC!$B$10)^H6</f>
+        <v/>
+      </c>
+      <c r="I7" s="32">
+        <f>1/(1+WACC!$B$10)^I6</f>
+        <v/>
+      </c>
+      <c r="J7" s="32">
+        <f>1/(1+WACC!$B$10)^J6</f>
+        <v/>
+      </c>
+      <c r="K7" s="32">
+        <f>1/(1+WACC!$B$10)^K6</f>
         <v/>
       </c>
     </row>
@@ -5294,24 +5540,44 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="19">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="19">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="19">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="19">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="19">
         <f>F5*F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="19">
+        <f>G5*G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="19">
+        <f>H5*H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="19">
+        <f>I5*I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="19">
+        <f>J5*J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="19">
+        <f>K5*K7</f>
         <v/>
       </c>
     </row>
@@ -5321,8 +5587,8 @@
           <t>PV of explicit FCFF</t>
         </is>
       </c>
-      <c r="B10" s="13">
-        <f>SUM(B8:F8)</f>
+      <c r="B10" s="19">
+        <f>SUM(B8:K8)</f>
         <v/>
       </c>
     </row>
@@ -5332,8 +5598,8 @@
           <t>Terminal NOPAT (FYn)</t>
         </is>
       </c>
-      <c r="B11" s="27">
-        <f>Model!J11</f>
+      <c r="B11" s="23">
+        <f>Model!O11</f>
         <v/>
       </c>
     </row>
@@ -5343,7 +5609,7 @@
           <t>Invested capital (mm)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="18" t="n">
         <v>105777</v>
       </c>
     </row>
@@ -5353,8 +5619,8 @@
           <t>Terminal invested capital (scaled w/ revenue)</t>
         </is>
       </c>
-      <c r="B13" s="27">
-        <f>$B$12*Model!J5/Model!E5</f>
+      <c r="B13" s="23">
+        <f>$B$12*Model!O5/Model!E5</f>
         <v/>
       </c>
     </row>
@@ -5364,7 +5630,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="12">
         <f>MAX($B$11/$B$13,WACC!$B$10)</f>
         <v/>
       </c>
@@ -5375,7 +5641,7 @@
           <t>Terminal reinvestment rate (g/ROIC)</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="33">
         <f>Assumptions!$B$22/$B$14</f>
         <v/>
       </c>
@@ -5386,7 +5652,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="19">
         <f>$B$11*(1+Assumptions!$B$22)*(1-$B$15)/(WACC!$B$10-Assumptions!$B$22)</f>
         <v/>
       </c>
@@ -5397,8 +5663,8 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B17" s="13">
-        <f>$B$16/(1+WACC!$B$10)^(5-0.5)</f>
+      <c r="B17" s="19">
+        <f>$B$16/(1+WACC!$B$10)^(10-0.5)</f>
         <v/>
       </c>
     </row>
@@ -5408,18 +5674,18 @@
           <t>TV as % of EV</t>
         </is>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="12">
         <f>$B$17/($B$10+$B$17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="30">
         <f>$B$10+$B$17</f>
         <v/>
       </c>
@@ -5430,7 +5696,7 @@
           <t>(−) Net debt</t>
         </is>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="23">
         <f>-Assumptions!$B$10</f>
         <v/>
       </c>
@@ -5441,40 +5707,40 @@
           <t>(−) Minority interest</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="23">
         <f>-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="30">
         <f>$B$20-Assumptions!$B$10-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Value per share</t>
         </is>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="34">
         <f>$B$23/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Upside vs price</t>
         </is>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="35">
         <f>$B$24/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -5516,149 +5782,149 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="11" t="n">
         <v>0.015</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="11" t="n">
         <v>0.025</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="11" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>0.1294780679678906</v>
+      <c r="A5" s="15" t="n">
+        <v>0.0994430166080667</v>
       </c>
       <c r="B5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>0.1369780679678906</v>
+      <c r="A6" s="15" t="n">
+        <v>0.1069430166080667</v>
       </c>
       <c r="B6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>0.1444780679678906</v>
+      <c r="A7" s="15" t="n">
+        <v>0.1144430166080667</v>
       </c>
       <c r="B7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>0.1519780679678906</v>
+      <c r="A8" s="15" t="n">
+        <v>0.1219430166080667</v>
       </c>
       <c r="B8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>0.1594780679678906</v>
+      <c r="A9" s="15" t="n">
+        <v>0.1294430166080667</v>
       </c>
       <c r="B9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -5694,7 +5960,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-08 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -5736,16 +6002,16 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>-284.13</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5755,17 +6021,17 @@
           <t>Tax Rate For Calcs</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
-        <v>2.1e-07</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>1.2e-07</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>1.32649e-07</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>1.5117e-07</v>
+      <c r="C6" s="25" t="n">
+        <v>2.1e-13</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>1.2e-13</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>1.32649e-13</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>1.5117e-13</v>
       </c>
     </row>
     <row r="7">
@@ -5774,16 +6040,16 @@
           <t>Normalized EBITDA</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>7339</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>35583</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>86137</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>144552</v>
       </c>
     </row>
@@ -5793,16 +6059,16 @@
           <t>Total Unusual Items</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>-1353</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5812,16 +6078,16 @@
           <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>-1353</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5831,16 +6097,16 @@
           <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>4368</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>29760</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>72880</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>120067</v>
       </c>
     </row>
@@ -5850,16 +6116,16 @@
           <t>Reconciled Depreciation</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>1543</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>1508</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>1864</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>2843</v>
       </c>
     </row>
@@ -5869,16 +6135,16 @@
           <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>11618</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>16621</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>32639</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>62475</v>
       </c>
     </row>
@@ -5888,16 +6154,16 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>5986</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>35583</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>86137</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>144552</v>
       </c>
     </row>
@@ -5907,16 +6173,16 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>4443</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>34075</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>84273</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>141709</v>
       </c>
     </row>
@@ -5926,16 +6192,16 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>609</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>1539</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>2041</v>
       </c>
     </row>
@@ -5945,16 +6211,16 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>262</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>257</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>247</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>259</v>
       </c>
     </row>
@@ -5964,16 +6230,16 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>267</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>866</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>1786</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>2300</v>
       </c>
     </row>
@@ -5983,16 +6249,16 @@
           <t>Normalized Income</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>5436.87</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>29760</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>72880</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>120067</v>
       </c>
     </row>
@@ -6002,16 +6268,16 @@
           <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>4368</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>29760</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>72880</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>120067</v>
       </c>
     </row>
@@ -6021,16 +6287,16 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>21397</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>27950</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>49044</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>85551</v>
       </c>
     </row>
@@ -6040,16 +6306,16 @@
           <t>Total Operating Income As Reported</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>4224</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>32972</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>81453</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>130387</v>
       </c>
     </row>
@@ -6059,16 +6325,16 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>25070</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>24940</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>24804</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>24514</v>
       </c>
     </row>
@@ -6078,16 +6344,16 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>24870</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>24690</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>24555</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>24359</v>
       </c>
     </row>
@@ -6097,17 +6363,17 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
-        <v>1.74e-07</v>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>1.19e-06</v>
-      </c>
-      <c r="E24" s="29" t="n">
-        <v>2.94e-06</v>
-      </c>
-      <c r="F24" s="29" t="n">
-        <v>4.900000000000001e-06</v>
+      <c r="C24" s="25" t="n">
+        <v>1.74e-13</v>
+      </c>
+      <c r="D24" s="25" t="n">
+        <v>1.19e-12</v>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>2.94e-12</v>
+      </c>
+      <c r="F24" s="25" t="n">
+        <v>4.900000000000001e-12</v>
       </c>
     </row>
     <row r="25">
@@ -6116,17 +6382,17 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
-        <v>1.76e-07</v>
-      </c>
-      <c r="D25" s="29" t="n">
-        <v>1.21e-06</v>
-      </c>
-      <c r="E25" s="29" t="n">
-        <v>2.97e-06</v>
-      </c>
-      <c r="F25" s="29" t="n">
-        <v>4.929999999999999e-06</v>
+      <c r="C25" s="25" t="n">
+        <v>1.76e-13</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>1.21e-12</v>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>2.97e-12</v>
+      </c>
+      <c r="F25" s="25" t="n">
+        <v>4.929999999999999e-12</v>
       </c>
     </row>
     <row r="26">
@@ -6135,16 +6401,16 @@
           <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>4368</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>29760</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>72880</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>120067</v>
       </c>
     </row>
@@ -6154,16 +6420,16 @@
           <t>Net Income Common Stockholders</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>4368</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>29760</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>72880</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>120067</v>
       </c>
     </row>
@@ -6173,16 +6439,16 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>4368</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>29760</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>72880</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>120067</v>
       </c>
     </row>
@@ -6192,16 +6458,16 @@
           <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>4368</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>29760</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>72880</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>120067</v>
       </c>
     </row>
@@ -6211,16 +6477,16 @@
           <t>Net Income Continuous Operations</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>4368</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>29760</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="25" t="n">
         <v>72880</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="25" t="n">
         <v>120067</v>
       </c>
     </row>
@@ -6230,16 +6496,16 @@
           <t>Tax Provision</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>-187</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>4058</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>11146</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>21383</v>
       </c>
     </row>
@@ -6249,16 +6515,16 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>4181</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>33818</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>84026</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>141450</v>
       </c>
     </row>
@@ -6268,16 +6534,16 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>-1401</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>237</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>1034</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>9022</v>
       </c>
     </row>
@@ -6287,16 +6553,16 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>-48</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>237</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>1034</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>9022</v>
       </c>
     </row>
@@ -6306,16 +6572,16 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>-1353</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6325,16 +6591,16 @@
           <t>Restructuring And Mergern Acquisition</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>1353</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6344,16 +6610,16 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>609</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>1539</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>2041</v>
       </c>
     </row>
@@ -6363,16 +6629,16 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>262</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>257</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>247</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>259</v>
       </c>
     </row>
@@ -6382,16 +6648,16 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>267</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>866</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>1786</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="25" t="n">
         <v>2300</v>
       </c>
     </row>
@@ -6401,16 +6667,16 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>5577</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>32972</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="25" t="n">
         <v>81453</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>130387</v>
       </c>
     </row>
@@ -6420,16 +6686,16 @@
           <t>Operating Expense</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>9779</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>11329</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>16405</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>23076</v>
       </c>
     </row>
@@ -6439,16 +6705,16 @@
           <t>Research And Development</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>7339</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>8675</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="25" t="n">
         <v>12914</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="25" t="n">
         <v>18497</v>
       </c>
     </row>
@@ -6458,16 +6724,16 @@
           <t>Selling General And Administration</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>2440</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>2654</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="25" t="n">
         <v>3491</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>4579</v>
       </c>
     </row>
@@ -6477,16 +6743,16 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>15356</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>44301</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>97858</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>153463</v>
       </c>
     </row>
@@ -6496,16 +6762,16 @@
           <t>Cost Of Revenue</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>11618</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>16621</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>32639</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>62475</v>
       </c>
     </row>
@@ -6515,16 +6781,16 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>26974</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>60922</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>130497</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>215938</v>
       </c>
     </row>
@@ -6534,16 +6800,16 @@
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>26974</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>60922</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="25" t="n">
         <v>130497</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="25" t="n">
         <v>215938</v>
       </c>
     </row>

--- a/docs/reports/NVDA.xlsx
+++ b/docs/reports/NVDA.xlsx
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>270.3735326589133</v>
+        <v>278.6125740277354</v>
       </c>
     </row>
     <row r="8">
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>197.12664298595</v>
+        <v>219.4886959810862</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>176.7483467801727</v>
+        <v>197.2306587063528</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>219.4191710831196</v>
+        <v>243.7528601513378</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>0.3888888888888889</v>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>270.3735326589133</v>
+        <v>278.6125740277354</v>
       </c>
     </row>
     <row r="20">
@@ -3596,7 +3596,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Target anchored 15% to the Street consensus ($301.62); model-only target $264.86.</t>
+          <t>Target anchored 15% to the Street consensus ($301.62); model-only target $274.55.</t>
         </is>
       </c>
     </row>
@@ -3708,31 +3708,31 @@
         <v>554440</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>645806.0994400255</v>
+        <v>644690.511111111</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>726668.3413311919</v>
+        <v>738528.796617284</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>797037.8965057848</v>
+        <v>833306.6588498354</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>858010.523282606</v>
+        <v>925896.2876109283</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>911136.9650182693</v>
+        <v>1012827.661281066</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>958029.1498762461</v>
+        <v>1090477.781979281</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>1000155.99589244</v>
+        <v>1155300.627908049</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>1038762.787695176</v>
+        <v>1204079.987753055</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>1064731.857387555</v>
+        <v>1234181.987446881</v>
       </c>
     </row>
     <row r="6">
@@ -3877,31 +3877,31 @@
         <v>309059.96</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>356419.5348501363</v>
+        <v>355803.4559394382</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>397016.3740161437</v>
+        <v>403500.0104354945</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>431032.5376173494</v>
+        <v>450656.6306768113</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>459230.6202960665</v>
+        <v>495582.66557914</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>482589.8319678983</v>
+        <v>536476.0099941769</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>502086.8145026244</v>
+        <v>571531.8814603315</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>518588.0106189381</v>
+        <v>599066.3761032427</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>538614.5591402202</v>
+        <v>624369.7533370865</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>552085.5265519732</v>
+        <v>639984.6006037613</v>
       </c>
     </row>
     <row r="10">
@@ -3961,31 +3961,31 @@
         <v>256407.5697703674</v>
       </c>
       <c r="C12" s="20" t="n">
-        <v>338948.2586116076</v>
+        <v>338500.0115237773</v>
       </c>
       <c r="D12" s="20" t="n">
-        <v>380873.3017311503</v>
+        <v>385418.1955725193</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>416356.6828550179</v>
+        <v>432265.1594617677</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>445983.7109139795</v>
+        <v>477436.93248379</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>470646.8302946997</v>
+        <v>519193.7279134119</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>491295.3462942344</v>
+        <v>555759.617347345</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>508801.4578386336</v>
+        <v>585438.9955838857</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>529707.2972319083</v>
+        <v>613465.950900647</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>545440.9956541875</v>
+        <v>632282.6047517705</v>
       </c>
     </row>
     <row r="13">
@@ -4319,28 +4319,28 @@
         <v>1.567588844946235</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>0.1647898770651929</v>
+        <v>0.1627777777777778</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.125211331948214</v>
+        <v>0.1455555555555555</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.09683861422348755</v>
+        <v>0.1283333333333334</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.07649903102992379</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.06191817034179282</v>
+        <v>0.09388888888888888</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.05146557176180035</v>
+        <v>0.07666666666666667</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.04397240524636979</v>
+        <v>0.05944444444444445</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.03860077024113361</v>
+        <v>0.04222222222222223</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>0.025</v>
